--- a/Planning.xlsx
+++ b/Planning.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\nir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A8A7FB5-DFF8-4A92-BB52-251A40B1F444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78DADF42-F00A-43D5-B734-12605E3D405A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="761" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="761" firstSheet="6" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MF_Summary" sheetId="1" r:id="rId1"/>
@@ -606,7 +606,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2519" uniqueCount="1221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2522" uniqueCount="1223">
   <si>
     <t>Aditya Birla Sun Life Balanced 95 Fund</t>
   </si>
@@ -4322,6 +4322,12 @@
   </si>
   <si>
     <t>342*0.5rs</t>
+  </si>
+  <si>
+    <t>github</t>
+  </si>
+  <si>
+    <t>https://github.com/niranjanadatta</t>
   </si>
 </sst>
 </file>
@@ -22561,23 +22567,16 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="U75:W75"/>
-    <mergeCell ref="U64:W64"/>
-    <mergeCell ref="AO1:AQ1"/>
-    <mergeCell ref="AT1:AV1"/>
-    <mergeCell ref="P1:R1"/>
-    <mergeCell ref="U1:W1"/>
-    <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="AE1:AG1"/>
-    <mergeCell ref="AJ1:AL1"/>
-    <mergeCell ref="P75:R75"/>
-    <mergeCell ref="P52:R52"/>
-    <mergeCell ref="U52:W52"/>
-    <mergeCell ref="F52:H52"/>
-    <mergeCell ref="K52:M52"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="A102:C102"/>
+    <mergeCell ref="F92:H92"/>
+    <mergeCell ref="K92:M92"/>
+    <mergeCell ref="P92:R92"/>
+    <mergeCell ref="F75:H75"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="K75:M75"/>
+    <mergeCell ref="A92:C92"/>
+    <mergeCell ref="F102:H102"/>
+    <mergeCell ref="K102:M102"/>
     <mergeCell ref="K64:M64"/>
     <mergeCell ref="F64:H64"/>
     <mergeCell ref="A64:C64"/>
@@ -22594,16 +22593,23 @@
     <mergeCell ref="A52:C52"/>
     <mergeCell ref="A35:C35"/>
     <mergeCell ref="AY1:BA1"/>
-    <mergeCell ref="A102:C102"/>
-    <mergeCell ref="F92:H92"/>
-    <mergeCell ref="K92:M92"/>
-    <mergeCell ref="P92:R92"/>
-    <mergeCell ref="F75:H75"/>
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="K75:M75"/>
-    <mergeCell ref="A92:C92"/>
-    <mergeCell ref="F102:H102"/>
-    <mergeCell ref="K102:M102"/>
+    <mergeCell ref="F52:H52"/>
+    <mergeCell ref="K52:M52"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="U75:W75"/>
+    <mergeCell ref="U64:W64"/>
+    <mergeCell ref="AO1:AQ1"/>
+    <mergeCell ref="AT1:AV1"/>
+    <mergeCell ref="P1:R1"/>
+    <mergeCell ref="U1:W1"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="AE1:AG1"/>
+    <mergeCell ref="AJ1:AL1"/>
+    <mergeCell ref="P75:R75"/>
+    <mergeCell ref="P52:R52"/>
+    <mergeCell ref="U52:W52"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -23352,6 +23358,17 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C45" t="s">
         <v>54</v>
       </c>
     </row>
@@ -33546,14 +33563,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="I12:N12"/>
-    <mergeCell ref="A204:F204"/>
-    <mergeCell ref="A97:F97"/>
-    <mergeCell ref="A138:F138"/>
-    <mergeCell ref="A151:F151"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A74:F74"/>
     <mergeCell ref="A210:F210"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A157:F157"/>
@@ -33565,6 +33574,14 @@
     <mergeCell ref="A53:F53"/>
     <mergeCell ref="A57:F57"/>
     <mergeCell ref="A177:F177"/>
+    <mergeCell ref="I12:N12"/>
+    <mergeCell ref="A204:F204"/>
+    <mergeCell ref="A97:F97"/>
+    <mergeCell ref="A138:F138"/>
+    <mergeCell ref="A151:F151"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A74:F74"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E30" location="MF_Summary!G7" display="MF_Summary!G7" xr:uid="{00000000-0004-0000-0100-000000000000}"/>

--- a/Planning.xlsx
+++ b/Planning.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\nir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78DADF42-F00A-43D5-B734-12605E3D405A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F937FA70-007C-492F-A6EA-B45E25DE132E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="761" firstSheet="6" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" tabRatio="761" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MF_Summary" sheetId="1" r:id="rId1"/>
@@ -22567,16 +22567,23 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A102:C102"/>
-    <mergeCell ref="F92:H92"/>
-    <mergeCell ref="K92:M92"/>
-    <mergeCell ref="P92:R92"/>
-    <mergeCell ref="F75:H75"/>
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="K75:M75"/>
-    <mergeCell ref="A92:C92"/>
-    <mergeCell ref="F102:H102"/>
-    <mergeCell ref="K102:M102"/>
+    <mergeCell ref="U75:W75"/>
+    <mergeCell ref="U64:W64"/>
+    <mergeCell ref="AO1:AQ1"/>
+    <mergeCell ref="AT1:AV1"/>
+    <mergeCell ref="P1:R1"/>
+    <mergeCell ref="U1:W1"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="AE1:AG1"/>
+    <mergeCell ref="AJ1:AL1"/>
+    <mergeCell ref="P75:R75"/>
+    <mergeCell ref="P52:R52"/>
+    <mergeCell ref="U52:W52"/>
+    <mergeCell ref="F52:H52"/>
+    <mergeCell ref="K52:M52"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="K1:M1"/>
     <mergeCell ref="K64:M64"/>
     <mergeCell ref="F64:H64"/>
     <mergeCell ref="A64:C64"/>
@@ -22593,23 +22600,16 @@
     <mergeCell ref="A52:C52"/>
     <mergeCell ref="A35:C35"/>
     <mergeCell ref="AY1:BA1"/>
-    <mergeCell ref="F52:H52"/>
-    <mergeCell ref="K52:M52"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="K1:M1"/>
-    <mergeCell ref="U75:W75"/>
-    <mergeCell ref="U64:W64"/>
-    <mergeCell ref="AO1:AQ1"/>
-    <mergeCell ref="AT1:AV1"/>
-    <mergeCell ref="P1:R1"/>
-    <mergeCell ref="U1:W1"/>
-    <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="AE1:AG1"/>
-    <mergeCell ref="AJ1:AL1"/>
-    <mergeCell ref="P75:R75"/>
-    <mergeCell ref="P52:R52"/>
-    <mergeCell ref="U52:W52"/>
+    <mergeCell ref="A102:C102"/>
+    <mergeCell ref="F92:H92"/>
+    <mergeCell ref="K92:M92"/>
+    <mergeCell ref="P92:R92"/>
+    <mergeCell ref="F75:H75"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="K75:M75"/>
+    <mergeCell ref="A92:C92"/>
+    <mergeCell ref="F102:H102"/>
+    <mergeCell ref="K102:M102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -33563,6 +33563,14 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="I12:N12"/>
+    <mergeCell ref="A204:F204"/>
+    <mergeCell ref="A97:F97"/>
+    <mergeCell ref="A138:F138"/>
+    <mergeCell ref="A151:F151"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A74:F74"/>
     <mergeCell ref="A210:F210"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A157:F157"/>
@@ -33574,14 +33582,6 @@
     <mergeCell ref="A53:F53"/>
     <mergeCell ref="A57:F57"/>
     <mergeCell ref="A177:F177"/>
-    <mergeCell ref="I12:N12"/>
-    <mergeCell ref="A204:F204"/>
-    <mergeCell ref="A97:F97"/>
-    <mergeCell ref="A138:F138"/>
-    <mergeCell ref="A151:F151"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A74:F74"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E30" location="MF_Summary!G7" display="MF_Summary!G7" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
@@ -39497,7 +39497,7 @@
       <c r="E2" s="4"/>
       <c r="F2" s="4">
         <f>SUM(D29)</f>
-        <v>30447182.289999999</v>
+        <v>30447363.289999999</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
@@ -40248,7 +40248,7 @@
         <v>1050</v>
       </c>
       <c r="D17" s="180">
-        <v>-1733.71</v>
+        <v>-1552.71</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
@@ -40574,11 +40574,11 @@
       </c>
       <c r="D29" s="204">
         <f>SUM(D2:D28)</f>
-        <v>30447182.289999999</v>
+        <v>30447363.289999999</v>
       </c>
       <c r="F29" s="4">
         <f>SUM(F2:F26)</f>
-        <v>32557988.289999999</v>
+        <v>32558169.289999999</v>
       </c>
       <c r="H29" s="116"/>
       <c r="J29" s="1">
@@ -40614,7 +40614,7 @@
       <c r="D31" s="4"/>
       <c r="F31">
         <f>SUM(F29:F30)</f>
-        <v>35473368.289999999</v>
+        <v>35473549.289999999</v>
       </c>
       <c r="J31" s="1">
         <v>41244</v>
